--- a/docs/testes/cenarios-complementares.xlsx
+++ b/docs/testes/cenarios-complementares.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenários QA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cenários QA'!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cenários QA'!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,8 +142,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CenariosComplementares" displayName="CenariosComplementares" ref="A1:K32" headerRowCount="1">
-  <autoFilter ref="A1:K32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CenariosComplementares" displayName="CenariosComplementares" ref="A1:K37" headerRowCount="1">
+  <autoFilter ref="A1:K37"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Cenário"/>
     <tableColumn id="2" name="Pré-requisito"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -526,15 +526,302 @@
     <row r="2" ht="180" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">CT-001: carrega a página inicial e apresenta o conteúdo principal</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Abrir a URL da página inicial.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A página inicial abre e apresenta conteúdo, sem falhas que impeçam a navegação ou a leitura do menu.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2497 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-001 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="180" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-002 acceptance: Poppins Regular e Medium carregam sem erro</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Abrir a página inicial e filtrar as requisições por `Poppins-Regular.otf` e `Poppins-Medium.otf`.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reproduzir e registrar o estado atual, sem presumir resultado além das evidências existentes.
+As URLs corretas das duas fontes respondem com sucesso, sem 404; o navegador não marca as fontes como erro.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1275 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-002 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="180" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-003 acceptance: não solicita /img e mantém os elementos dos depoimentos carregados</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Abrir a página inicial.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nenhuma requisição para `/img`; o card mede 390 × 390 px, tem raio de 120 px, cor `#ffe8a3`, posição absoluta à esquerda; `pizzas.png` carrega sem erro.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1526 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-003 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="180" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-004 acceptance: nenhum recurso solicitado responde 404</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Carregar a página inicial.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificar e documentar as falhas existentes sem classificá-las como resolvidas.
+Nenhuma requisição de recurso esperado retorna `404`; demais recursos são avaliados conforme o status esperado para cada tipo.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 823 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-004 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="180" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-005: mantém os oito produtos visíveis com nomes, preços e imagens carregadas</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Carregar a página inicial antes de eventual correção e registrar produtos, nomes, preços e imagens visíveis.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Os produtos que a aplicação deve apresentar continuam visíveis, com nomes e preços, e suas imagens esperadas carregam antes e depois da correção.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2719 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-005 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="180" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">CT-006 — Navegar pelas âncoras da página</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview disponível; página inicial carregada.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Ativar Reservas.
 2. Conferir URL e seção alcançada.
@@ -542,59 +829,59 @@
 4. Voltar ao início pela navegação disponível.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cada link aponta para uma Ã¢ncora existente e leva Ã  seÃ§Ã£o correspondente, sem erro de navegaÃ§Ã£o.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2066 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada link aponta para uma âncora existente e leva à seção correspondente, sem erro de navegação.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3738 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura NAV-01. A exploração via MCP confirmou apenas a âncora Cardápio. Origem: `docs/auditoria/mapa-de-fluxos.md`; `app/index.html`.</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-006 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="180" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="8" ht="180" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-007 — Abrir e fechar a navegação mobile</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; viewport de 390 × 844 px; página inicial carregada.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Redimensionar para 390 × 844 px.
 2. Ativar o botão do menu.
@@ -603,119 +890,118 @@
 5. Abrir uma seção usando um link.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O menu alterna entre fechado e aberto; os links ficam operÃ¡veis quando aberto e navegam para suas Ã¢ncoras.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2842 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O menu alterna entre fechado e aberto; os links ficam operáveis quando aberto e navegam para suas âncoras.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3608 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura NAV-02. A abertura foi observada na auditoria, mas este cenário não foi repetido nesta solicitação. Origem: `docs/auditoria/inventario-funcional.md`; `app/css/responsivo.css`.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-007 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="9" ht="180" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-008 — Conferir conteúdo das seções institucionais</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; conteúdo aprovado pelo responsável do produto disponível.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Abrir Serviços, banner, Reservas e rodapé.
-2. Comparar textos, imagens e links com o conteúdo aprovado.
-3. Conferir se âncoras internas apontam para destinos existentes.
-4. Não abrir destinos externos.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Abrir a página local.
+2. Conferir título e conteúdo não vazio em Serviços, Cardápio, Depoimentos e Reservas.
+3. Confirmar que a navegação aponta para cada seção existente.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BAIXA</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ConteÃºdo e destinos internos correspondem Ã  referÃªncia aprovada. O conjunto de textos aprovado ainda precisa ser fornecido.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a referÃªncia aprovada de textos, imagens e destinos institucionais ainda nÃ£o foi fornecida.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As seções Serviços, Cardápio, Depoimentos e Reservas existem, têm título e conteúdo não vazio; os links internos de navegação apontam para destinos existentes. A verificação é estrutural e de regressão.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 4085 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura de conteúdo estático. Não fixar textos ou destinos atuais como regra comercial sem confirmação. Origem: `docs/auditoria/matriz-de-cobertura.md`; pergunta 15 e perguntas 16–17 em `docs/auditoria/perguntas-pendentes.md`.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-008 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="180" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-008 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="180" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-009 — Exibir produtos ao trocar de categoria</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; catálogo carregado; lista inicial conhecida para as seis categorias.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Selecionar Burgers, Pizzas, Churrasco, Steaks, Bebidas e Sobremesas, uma por vez.
 2. Conferir categoria ativa e quantidade de cards em cada seleção.
@@ -723,59 +1009,59 @@
 4. Não tratar nomes e preços como dados comerciais aprovados.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A categoria selecionada substitui a anterior e mostra oito cards iniciais, conforme o comportamento documentado. Imagens dos cards exibidos carregam.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 7193 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 9118 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CAT-01; CT-005 cobre somente os oito produtos iniciais de Burgers. Catálogo comercial e preços aguardam confirmação (perguntas 11–13). Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/dados.js`.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-009 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="180" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="11" ht="180" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-010 — Expandir a lista de produtos</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; categoria Pizzas selecionada; estado inicial com oito cards.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Conferir a quantidade inicial de cards.
 2. Ativar Ver mais uma vez.
@@ -783,59 +1069,59 @@
 4. Tentar localizar duplicidades.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A lista passa de oito para doze cards, sem duplicidades, e Ver mais deixa de ser exibido.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 4892 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3245 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CAT-02. O comportamento 8 → 12 foi observado na auditoria anterior, sem execução formal registrada nesta solicitação. Origem: `docs/auditoria/mapa-de-fluxos.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-010 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="180" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="12" ht="180" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-011 — Trocar de categoria após expandir</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; catálogo carregado; categoria Pizzas com lista expandida.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Expandir Pizzas.
 2. Selecionar Burgers.
@@ -843,59 +1129,59 @@
 4. Conferir que os cards de Pizzas não permaneceram na lista.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PASSOU</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A troca limpa os cards anteriores, apresenta os oito primeiros da nova categoria e restaura Ver mais quando aplicÃ¡vel.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 5015 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A troca limpa os cards anteriores, apresenta os oito primeiros da nova categoria e restaura Ver mais quando aplicável.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: expect(locator).toBeVisible() failed.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CAT-03; a auditoria observou a volta para oito cards ao trocar de categoria. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-011 (PASSOU); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="180" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-011 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-012 — Impedir quantidade negativa no produto</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; card de produto visível; seletor iniciado em zero.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Ativar diminuir com quantidade zero.
 2. Conferir o valor exibido.
@@ -903,118 +1189,118 @@
 4. Conferir o valor após cada ação.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A quantidade nÃ£o fica abaixo de zero; incrementar e diminuir atualizam o valor do seletor.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3177 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A quantidade não fica abaixo de zero; incrementar e diminuir atualizam o valor do seletor.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3075 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura PROD-01. Regra identificada no código, ainda sem execução formal. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-012 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="180" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="14" ht="180" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-013 — Não adicionar produto com quantidade zero</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; carrinho vazio; card de produto visível e quantidade igual a zero.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Registrar badge e conteúdo do carrinho.
 2. Ativar adicionar sem incrementar a quantidade.
 3. Conferir badge, conteúdo do carrinho e estado do seletor.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carrinho e badge permanecem inalterados; nenhuma linha de produto Ã© criada.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2530 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carrinho e badge permanecem inalterados; nenhuma linha de produto é criada.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3174 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura PROD-02. A regra está indicada no código; nenhuma confirmação visual foi coletada nesta solicitação. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-013 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="180" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15" ht="180" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-014 — Somar adições repetidas do mesmo produto</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; carrinho vazio; produto de catálogo disponível.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Selecionar duas unidades do produto e adicionar.
 2. Selecionar mais uma unidade do mesmo produto e adicionar novamente.
@@ -1022,59 +1308,59 @@
 4. Conferir badge, quantidade e número de linhas do produto.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O carrinho contÃ©m uma linha para o produto com quantidade total trÃªs; badge e seletor apÃ³s cada adiÃ§Ã£o refletem o estado documentado.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 8771 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O carrinho contém uma linha para o produto com quantidade total três; badge e seletor após cada adição refletem o estado documentado.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 7481 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura PROD-03. Repetição e mescla estão descritas no código, mas a auditoria confirmou somente uma adição. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-014 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="180" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="16" ht="180" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-015 — Bloquear avanço com carrinho vazio</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; carrinho vazio; modal fechado.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Abrir Meu carrinho.
 2. Conferir o estado vazio.
@@ -1082,59 +1368,59 @@
 4. Conferir etapa e mensagem exibida.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O carrinho informa que estÃ¡ vazio e nÃ£o avanÃ§a para endereÃ§o.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1839 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O carrinho informa que está vazio e não avança para endereço.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1302 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CART-01. A auditoria observou o bloqueio no site publicado; esta linha ainda não representa execução de teste. Origem: `docs/auditoria/mapa-de-fluxos.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-015 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="180" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="17" ht="180" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-016 — Alterar e remover itens no carrinho</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; adicionar itens com dados sintéticos em estado isolado.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Abrir o carrinho com dois produtos.
 2. Aumentar e diminuir a quantidade de um deles.
@@ -1143,300 +1429,295 @@
 5. Conferir lista, badge e estado vazio em cada transição.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quantidades, linhas e badge permanecem coerentes; item com quantidade zero desaparece; a remoÃ§Ã£o do Ãºltimo item apresenta o estado vazio.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3399 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantidades, linhas e badge permanecem coerentes; item com quantidade zero desaparece; a remoção do último item apresenta o estado vazio.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2901 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CART-02. Usar estado de navegador isolado e não depender de outro cenário. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-016 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="180" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="18" ht="180" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-017 — Conferir subtotal, entrega e total</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; carrinho isolado; preços observáveis dos itens selecionados.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Adicionar um item e conferir subtotal.
-2. Alterar quantidade e conferir recálculo.
-3. Adicionar ou remover outro item e conferir recálculo.
-4. Registrar entrega e total exibidos.
-5. Comparar a taxa com a regra comercial aprovada, se disponível.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Adicionar o primeiro produto com quantidade 2 e repetir com quantidade 1.
+2. Abrir o carrinho.
+3. Conferir quantidade, subtotal, taxa única de entrega e total conforme a linha de base.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Subtotal corresponde Ã  soma dos preÃ§os exibidos multiplicados pelas quantidades. Taxa e total devem seguir a regra de entrega aprovada; a taxa fixa de R$ 5,00 no cÃ³digo nÃ£o Ã©, por si sÃ³, requisito aprovado.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a taxa e a regra de cÃ¡lculo da entrega ainda nÃ£o foram confirmadas (pergunta 6 de perguntas-pendentes.md).</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O subtotal é a soma de preço unitário × quantidade. Para carrinho não vazio, a linha de base atual considera entrega fixa de R$ 5,00 por pedido, uma única vez, e total = subtotal + entrega, formatados em BRL com duas casas decimais.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 7316 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CART-03. Pergunta 6 em `docs/auditoria/perguntas-pendentes.md`; origem adicional: `app/js/app.js`. Não automatizar a taxa como valor comercial até confirmação.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-017 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="180" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-017 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="180" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-018 — Validar campos de endereço obrigatórios</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; carrinho com item sintético; etapa de endereço acessível.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Tentar avançar com todos os campos vazios.
-2. Repetir preenchendo um campo de cada vez com espaços.
-3. Registrar campo destacado, mensagem e foco após cada tentativa.
-4. Não usar dados pessoais reais.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Percorrer os campos obrigatórios, deixando cada um vazio ou com espaços.
+2. Tentar avançar à revisão.
+3. Conferir feedback e permanência na etapa de endereço.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O avanÃ§o deve seguir a lista de campos obrigatÃ³rios aprovada e identificar o primeiro campo invÃ¡lido. A lista e as mensagens ainda dependem de confirmaÃ§Ã£o.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a lista aprovada de campos e mensagens obrigatÃ³rios ainda nÃ£o foi definida (perguntas 3 e 10).</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEP, endereço, bairro, número, cidade e UF são obrigatórios. Campo vazio ou composto apenas por espaços impede a revisão, mostra feedback identificável e mantém o usuário na etapa de endereço. Complemento é opcional.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 6630 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura ADDR-01. Perguntas 3 e 10 em `docs/auditoria/perguntas-pendentes.md`; não converter a validação atual do código em requisito aprovado.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-018 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="180" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-018 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="180" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-019 — Rejeitar UF não selecionada</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; carrinho com item sintético; demais campos preenchidos com dados artificiais; UF permanece no placeholder.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Preencher os campos de endereço sem selecionar UF.
-2. Tentar avançar para a revisão.
-3. Registrar etapa, validação, mensagem e foco.
-4. Repetir selecionando uma UF válida após confirmação da regra.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Preencher os campos obrigatórios com valores sintéticos.
+2. Manter o placeholder de UF selecionado.
+3. Tentar avançar e conferir bloqueio e indicação do campo.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A revisÃ£o nÃ£o deve aceitar o valor placeholder como UF vÃ¡lida, caso a UF seja confirmada obrigatÃ³ria.</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a obrigatoriedade da seleÃ§Ã£o de UF aguarda decisÃ£o (pergunta 1).</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O placeholder de UF (`-1`) é inválido. A revisão só avança depois de selecionar uma UF brasileira válida (sigla de duas letras). O foco/feedback deve indicar a UF inválida.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: UF placeholder deve manter o usuário na etapa de endereço | Error: o foco deve ir ao seletor de UF | Error: expect(received).toMatch(expected).</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura ADDR-02; a auditoria registrou que o placeholder passou pela validação atual e classificou o comportamento como defeito. Confirmar requisito antes de usar resultado para aprovação. Origem: `docs/auditoria/perguntas-pendentes.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-019 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="180" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-019 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="180" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-020 — Validar formato de CEP preenchido manualmente</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; caminho de preenchimento manual; restante do formulário controlado.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Repetir o avanço com CEP vazio, sete dígitos, oito dígitos, nove dígitos e letras.
-2. Registrar o comportamento de cada valor.
-3. Não acionar ViaCEP neste cenário.
-4. Comparar com o formato aprovado pelo negócio quando definido.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Preencher os demais campos obrigatórios.
+2. Tentar CEP válido sem máscara, válido com máscara e formatos inválidos.
+3. Conferir normalização ou bloqueio, sem consultar ViaCEP.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CritÃ©rio para tamanho, hÃ­fen e caracteres aceitos depende da confirmaÃ§Ã£o do formato de CEP. AtÃ© lÃ¡, coletar observaÃ§Ãµes sem veredito de aceitaÃ§Ã£o.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: o formato e a aceitaÃ§Ã£o de CEP manual aguardam decisÃ£o (perguntas 2 e 10).</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O CEP manual aceita oito dígitos, com ou sem hífen único após o quinto dígito (`12345678` ou `12345-678`). A aplicação remove a máscara antes de montar o resumo. Letras, espaços internos, hífen em outra posição ou quantidade diferente de oito dígitos impedem a revisão. A validação manual não exige chamar ViaCEP.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: CEP 12345-678: resumo deve usar somente oito dígitos | Error: CEP 1234567: etapa de revisão esperada=false | Error: CEP 1234567: foco deve retornar ao campo | Error: CEP 1234567: deve haver mensagem de validação | Error: CEP 123456789: etapa de revisão esperada=false | Error: CEP 123456789: foco deve retornar ao campo | Error: CEP 123456789: deve haver mensagem de validação | Error: CEP 12A45678: etapa de revisão esperada=false | Error: CEP 12A45678: foco deve retornar ao campo | Error: CEP 12A45678: deve haver mensagem de validação | Error: CEP 12 345678: etapa de revisão esperada=false | Error: CEP 12 345678: foco deve retornar ao campo | Error: CEP 12 345678: deve haver mensagem de validação | Error: CEP 1234-5678: etapa de revisão esperada=false | Error: CEP 1234-5678: foco deve retornar ao campo | Error: CEP 1234-5678: deve haver mensagem de validação.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura ADDR-03. Perguntas 2 e 10 em `docs/auditoria/perguntas-pendentes.md`; auditoria identificou que o caminho manual só verifica campo não vazio.</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-020 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="180" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-020 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="180" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-021 — Preencher endereço com resposta ViaCEP controlada</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; rota ViaCEP interceptada; CEP sintético definido na fixture; formulário na etapa de endereço.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Interceptar a chamada de CEP com resposta de sucesso determinística.
 2. Informar o CEP sintético no formato aceito pela busca.
@@ -1445,361 +1726,354 @@
 5. Confirmar que nenhuma chamada real ao serviço foi feita.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Os campos mapeados pela integraÃ§Ã£o recebem os valores correspondentes da fixture; UF Ã© selecionada e o foco segue para nÃºmero, conforme implementaÃ§Ã£o documentada.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3119 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Os campos mapeados pela integração recebem os valores correspondentes da fixture; UF é selecionada e o foco segue para número, conforme implementação documentada.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2785 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura CEP-01. A auditoria confirma o mapeamento no código, não o funcionamento observado de ViaCEP. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-021 (PASSOU); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="180" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-022 — Tratar CEP não encontrado ou falha ViaCEP</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; chamada ViaCEP interceptada; fixtures para CEP não encontrado, erro HTTP e falha de rede/timeout.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Executar cada fixture em contexto isolado.
-2. Registrar feedback, estado de carregamento e valores preenchidos.
-3. Tentar continuar pelo preenchimento manual.
-4. Não depender do serviço público nem inventar texto de mensagem.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MAIOR</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mensagem, recuperaÃ§Ã£o e comportamento manual devem corresponder ao critÃ©rio aprovado. Esse critÃ©rio ainda nÃ£o estÃ¡ definido; atÃ© lÃ¡, o cenÃ¡rio Ã© exploratÃ³rio.</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: mensagem, retry e comportamento manual apÃ³s indisponibilidade do ViaCEP ainda aguardam decisÃ£o (pergunta 5).</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura CEP-02. Perguntas 4 e 5 em `docs/auditoria/perguntas-pendentes.md`; ausência de handler de falha identificada no código.</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-022 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="180" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-023 — Confirmar tratamento do complemento</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; carrinho com item sintético; requisitos dos demais campos definidos.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Preencher todos os campos obrigatórios sem complemento.
-2. Tentar avançar.
-3. Repetir deixando um campo obrigatório vazio.
-4. Comparar com a regra aprovada.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MENOR</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Complemento vazio sÃ³ deve ser aceito se sua condiÃ§Ã£o opcional for confirmada; os campos restantes devem seguir a lista obrigatÃ³ria aprovada.</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a obrigatoriedade e o tratamento do complemento ainda nÃ£o foram aprovados (pergunta 3).</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura ADDR-04. Pergunta 3 em `docs/auditoria/perguntas-pendentes.md`; o código sugere complemento opcional, mas isso não confirma a regra de negócio.</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-023 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="180" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-024 — Retornar à etapa de endereço durante a revisão</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; carrinho e endereço sintéticos válidos segundo regras aprovadas.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Avançar do endereço para a revisão.
-2. Voltar à etapa anterior.
-3. Conferir campos e carrinho.
-4. Alterar um campo e retornar à revisão.
-5. Conferir atualização sem duplicidade.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MENOR</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valores preservados ou limpos e atualizaÃ§Ã£o da revisÃ£o devem seguir uma regra de navegaÃ§Ã£o aprovada; nÃ£o presumir persistÃªncia entre etapas.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a preservaÃ§Ã£o ou limpeza dos campos ao voltar ainda nÃ£o foi definida (pergunta 9).</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura CHK-01. Pergunta 9 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/js/app.js`.</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-024 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="180" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-025 — Conferir preparo do link de pedido sem envio</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; dados sintéticos; destino de saída interceptado ou link inspecionado sem ativação.</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Preencher carrinho e endereço com valores artificiais válidos.
-2. Avançar até a revisão.
-3. Inspecionar href ou interceptar a abertura de nova página.
-4. Comparar telefone, itens, quantidades, endereço e total com o contrato aprovado.
-5. Não abrir WhatsApp nem enviar pedido.</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MAIOR</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O link e a mensagem devem corresponder ao contrato aprovado e nÃ£o devem enviar dados durante o teste. Destino e formato ainda dependem de decisÃ£o.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: destino aprovado e conteÃºdo exato da mensagem ainda nÃ£o foram definidos (perguntas 17â€“19).</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura ORDER-01. Perguntas 17–19 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/js/app.js`.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-025 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="180" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-026 — Conferir links de reserva e telefone sem ativá-los</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; página inicial carregada; sem abrir destinos externos.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Inspecionar os hrefs dos controles de reserva e telefone.
-2. Registrar esquema, destino e texto associado.
-3. Comparar com os números e mensagens oficiais aprovados.
-4. Não abrir WhatsApp nem iniciar chamada.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MENOR</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Os hrefs usam os destinos e formatos confirmados pelo responsÃ¡vel do produto. Os destinos atuais ainda nÃ£o foram aprovados.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: os destinos oficiais dos links de reserva e telefone ainda nÃ£o foram confirmados (perguntas 16â€“17).</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura RES-01. Perguntas 16–17 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/index.html`; `app/js/app.js`.</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-026 (PENDENTE); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
     <row r="23" ht="180" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">CT-022 — Tratar CEP não encontrado ou falha ViaCEP</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Interceptar ViaCEP com resposta de CEP inexistente.
+2. Interceptar a consulta seguinte com falha de rede.
+3. Conferir mensagens e possibilidade de preenchimento manual.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIOR</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resposta ViaCEP de CEP inexistente apresenta feedback que permita entender que a consulta não encontrou o CEP e que o preenchimento manual continua disponível. Falha de rede/timeout também deve apresentar feedback recuperável, manter o CEP e deixar o formulário utilizável. As respostas são mockadas; nenhum serviço público é chamado.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: falha de rede deve produzir feedback que permita recuperação.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura CEP-02. Perguntas 4 e 5 em `docs/auditoria/perguntas-pendentes.md`; ausência de handler de falha identificada no código.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-022 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="180" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-023 — Confirmar tratamento do complemento</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Concluir o endereço com complemento vazio e avançar.
+2. Repetir com complemento sintético preenchido.
+3. Conferir aceitação e preservação do valor.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENOR</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complemento vazio é aceito; quando preenchido, seu valor é preservado na revisão. Demais campos obrigatórios continuam validados.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 5832 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura ADDR-04. Pergunta 3 em `docs/auditoria/perguntas-pendentes.md`; o código sugere complemento opcional, mas isso não confirma a regra de negócio.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-023 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="180" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-024 — Retornar à etapa de endereço durante a revisão</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Adicionar produto e preencher o endereço com dados sintéticos.
+2. Avançar à revisão e voltar ao endereço.
+3. Conferir que endereço, carrinho e total foram preservados.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENOR</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ao voltar da revisão para o endereço, CEP, endereço, bairro, número, cidade, UF, complemento, itens do carrinho e total permanecem preenchidos, sem duplicação de itens.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 4756 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura CHK-01. Pergunta 9 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/js/app.js`.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-024 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="180" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-025 — Conferir preparo do link de pedido sem envio</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Preparar um pedido com endereço sintético.
+2. Abrir a revisão.
+3. Inspecionar o link wa.me e a mensagem codificada sem ativar o link.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIOR</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A etapa de revisão prepara um link HTTPS `wa.me` com o telefone configurado pela aplicação e uma mensagem codificada que contém itens, quantidades, preços, endereço sintético, CEP e total. O teste inspeciona o link, sem abri-lo nem enviar mensagem.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 3453 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura ORDER-01. Perguntas 17–19 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/js/app.js`.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-025 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="180" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-026 — Conferir links de reserva e telefone sem ativá-los</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Inspecionar os links de reserva e telefone no DOM.
+2. Conferir esquema e formato dos destinos.
+3. Não abrir, enviar ou iniciar chamada.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENOR</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O link de reserva usa HTTPS para `wa.me`, com telefone numérico e mensagem não vazia; o link de contato usa `tel:` com telefone numérico. Os destinos são inspecionados no DOM e nunca ativados.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1094 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura RES-01. Perguntas 16–17 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/index.html`; `app/js/app.js`.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-026 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="180" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">CT-027 — Trocar depoimento pelo seletor</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; seção Depoimentos carregada.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Ativar os seletores 1, 2 e 3, um por vez.
 2. Conferir relato visível e indicador ativo.
@@ -1807,59 +2081,59 @@
 4. Comparar o conteúdo com a versão aprovada quando disponível.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BAIXA</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TRIVIAL</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O relato selecionado e o indicador ativo correspondem ao seletor escolhido. O conteÃºdo comercial deve ser comparado com a referÃªncia aprovada, ainda pendente.</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2227 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O relato selecionado e o indicador ativo correspondem ao seletor escolhido. O conteúdo comercial deve ser comparado com a referência aprovada, ainda pendente.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1554 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura TESTI-01. A auditoria observou a troca dos seletores 2 e 3. Pergunta 15 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/index.html`; `app/js/app.js`.</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-027 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="180" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="29" ht="180" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-028 — Detectar erros de recursos ao percorrer a página</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ambiente local/preview; registro de rede iniciado antes da navegação.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Carregar a página inicial e registrar respostas HTTP.
 2. Percorrer as seções e carregar os recursos nelas referenciados.
@@ -1868,363 +2142,63 @@
 5. Verificar que bloqueios externos não impedem a navegação principal.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ALTA</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NÃO FUNCIONAL</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nenhum recurso necessÃ¡rio e esperado retorna erro inesperado; falhas externas controladas nÃ£o devem impedir conteÃºdo principal. CT-004 observa atualmente apenas recursos solicitados no carregamento inicial.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2030 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nenhum recurso necessário e esperado retorna erro inesperado; falhas externas controladas não devem impedir conteúdo principal. CT-004 observa atualmente apenas recursos solicitados no carregamento inicial.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1817 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura NET-03; complementar a CT-002, CT-003 e CT-004 sem substituir seus resultados históricos. Origem: `docs/auditoria/matriz-de-cobertura.md`; `tests/03-network/unexpected-404.spec.js`.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-028 (PASSOU); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="180" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-029 — Verificar layout em larguras representativas</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; viewport configurável; critérios visuais aprovados ou registrados como exploratórios.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Conferir a página e o carrinho em 390, 767, 768, 1024 e 1280 px.
-2. Verificar rolagem horizontal, clipping e controles essenciais.
-3. Repetir nas orientações e alturas acordadas.
-4. Registrar o viewport de cada divergência.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MENOR</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃO FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ConteÃºdo e controles essenciais devem permanecer utilizÃ¡veis sem clipping impeditivo. Viewports e tolerÃ¢ncias finais dependem de aprovaÃ§Ã£o do alvo responsivo.</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a matriz de viewports e as tolerÃ¢ncias de clipping ainda nÃ£o foram aprovadas.</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura RESP-01. A auditoria só observou 390 × 844 px. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/css/responsivo.css`.</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-029 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="180" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-030 — Acessar controles de produto por toque</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; emulação touchscreen confiável; viewport mobile; sem interação de hover de mouse.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Abrir o card de produto sem hover.
-2. Localizar os controles de quantidade e adição.
-3. Operar incremento, decremento e adição por toque.
-4. Conferir estado do card e badge do carrinho.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ALTA</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MAIOR</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Controles essenciais devem ser descobertos e operÃ¡veis por toque ou ter alternativa aprovada. O comportamento esperado em touchscreen ainda nÃ£o foi confirmado.</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a operaÃ§Ã£o esperada dos controles em touchscreen ainda nÃ£o foi confirmada (pergunta 23).</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura RESP-02. A auditoria identificou controles condicionados a hover e não confirmou o comportamento em toque. Pergunta 23 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/css/main.css`.</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-030 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="180" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-031 — Operar navegação e modal usando teclado</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; teclado; página inicial e modal do carrinho acessíveis.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Navegar com Tab e Shift+Tab pela página.
-2. Acionar links e controles com Enter ou Espaço conforme seu papel.
-3. Abrir e fechar o modal pelo teclado.
-4. Registrar foco visível, ordem, contenção e retorno de foco.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MAIOR</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃO FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AÃ§Ãµes essenciais devem ser alcanÃ§Ã¡veis e operÃ¡veis por teclado, com foco perceptÃ­vel e ordem utilizÃ¡vel. CritÃ©rios detalhados de acessibilidade aguardam definiÃ§Ã£o do alvo.</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: o alvo de acessibilidade e os critÃ©rios de foco, ordem e teclado ainda nÃ£o foram definidos (pergunta 22).</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura A11Y-01. Origem: `docs/auditoria/riscos-e-lacunas.md`; `app/index.html`; pergunta 22 em `docs/auditoria/perguntas-pendentes.md`.</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-031 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="180" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-032 — Conferir idioma, nomes acessíveis e rótulos</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; árvore de acessibilidade disponível; alvo de acessibilidade definido para avaliação de conformidade.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Conferir idioma declarado e idioma do conteúdo.
-2. Inspecionar nomes acessíveis de controles e imagens relevantes.
-3. Verificar associação entre rótulos e campos.
-4. Medir contraste somente com critério aprovado.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MÉDIA</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MENOR</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃO FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Idioma, nomes acessÃ­veis, rÃ³tulos e contraste devem atender ao padrÃ£o aprovado. Idioma esperado e alvo WCAG ainda dependem de confirmaÃ§Ã£o.</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: o idioma declarado e o padrÃ£o de acessibilidade esperado ainda nÃ£o foram aprovados (perguntas 20 e 22).</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura A11Y-02. Origem: `docs/auditoria/riscos-e-lacunas.md`; perguntas 20 e 22 em `docs/auditoria/perguntas-pendentes.md`.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-032 (PENDENTE); HTML fonte e detalhes no report.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="180" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT-033 — Verificar compatibilidade nos navegadores suportados</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente local/preview; lista de navegadores e versões aprovada; mesma versão da aplicação disponível.</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Executar os fluxos essenciais nos navegadores e versões acordados.
-2. Conferir catálogo, carrinho, etapas e layout.
-3. Registrar navegador, versão e divergências por fluxo.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAIXA</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MENOR</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃO FUNCIONAL</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Os fluxos essenciais funcionam nos navegadores oficialmente suportados. A lista de alvos ainda nÃ£o foi definida.</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a lista oficial de navegadores e versÃµes suportados ainda nÃ£o foi definida (pergunta 21).</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobertura BROWSER-01. A configuração atual executa Chromium. Pergunta 21 em `docs/auditoria/perguntas-pendentes.md`; origem: `playwright.config.js`.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-033 (PENDENTE); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
     <row r="30" ht="180" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CT-034 — Verificar exposição de endereço em logs e evidências</t>
+          <t xml:space="preserve">CT-029 — Verificar layout em larguras representativas</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ambiente local/preview; somente endereço e CEP sintéticos; política de logs e retenção definida.</t>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Preencher endereço sintético e chegar à revisão sem concluir pedido.
-2. Conferir console, relatório, screenshot e trace produzidos pelo cenário.
-3. Verificar se endereço ou CEP aparecem sem necessidade.
-4. Não usar dados pessoais reais.</t>
+          <t xml:space="preserve">1. Redimensionar a página para cada largura da matriz documentada.
+2. Medir largura do documento e da viewport.
+3. Registrar overflow acima da tolerância.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2234,7 +2208,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAIOR</t>
+          <t xml:space="preserve">MENOR</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2244,42 +2218,337 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDENTE</t>
+          <t xml:space="preserve">FALHOU</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logs e evidÃªncias devem seguir a polÃ­tica de minimizaÃ§Ã£o e retenÃ§Ã£o aprovada. A polÃ­tica ainda nÃ£o foi definida; a auditoria observou registro do texto do pedido no console.</t>
+          <t xml:space="preserve">A página não apresenta rolagem horizontal involuntária (tolerância de 1 CSS px) nas larguras 320, 360, 390, 768, 1024 e 1366 px. Os elementos principais do cenário devem caber na viewport.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: a polÃ­tica de logs, privacidade e retenÃ§Ã£o ainda nÃ£o foi definida (perguntas 25â€“26).</t>
+          <t xml:space="preserve">Falhou: Error: overflow horizontal em 320px | Error: overflow horizontal em 768px | Error: overflow horizontal em 1024px | Error: overflow horizontal em 1366px.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobertura SEC-01 de privacidade. Perguntas 25–26 em `docs/auditoria/perguntas-pendentes.md`; risco R-05 em `docs/auditoria/riscos-e-lacunas.md`; origem: `app/js/app.js`.</t>
+          <t xml:space="preserve">Cobertura RESP-01. A auditoria só observou 390 × 844 px. Origem: `docs/auditoria/matriz-de-cobertura.md`; `app/css/responsivo.css`.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card JPEG — CT-034 (PENDENTE); HTML fonte e detalhes no report.html</t>
+          <t xml:space="preserve">Card JPEG — CT-029 (FALHOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
     <row r="31" ht="180" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">CT-030 — Acessar controles de produto por toque</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Ativar viewport móvel com toque.
+2. Procurar controles de quantidade sem hover.
+3. Tocar para ajustar quantidade e adicionar produto.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTA</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIOR</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em contexto Chromium com toque habilitado e viewport 390 × 844, os controles de quantidade e adição são descobríveis e operáveis sem depender de hover. A interação deve atualizar quantidade/badge e permitir adicionar o produto.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: os controles devem ser descobríveis sem hover.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura RESP-02. A auditoria identificou controles condicionados a hover e não confirmou o comportamento em toque. Pergunta 23 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/css/main.css`.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-030 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="180" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-031 — Operar navegação e modal usando teclado</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Inspecionar foco dos controles principais.
+2. Usar teclado para abrir navegação e carrinho.
+3. Pressionar Escape e conferir fechamento do modal.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIOR</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NÃO FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navegação principal, abertura/fechamento do menu móvel, seletor de categoria, controles de produto, carrinho e ações de etapa exercitados no cenário devem ser alcançáveis e ativáveis por teclado. Escape deve fechar o modal quando ele estiver aberto.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: controles que alteram o estado precisam ser alcançáveis por teclado | Error: expect(locator).toBeHidden() failed.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura A11Y-01. Origem: `docs/auditoria/riscos-e-lacunas.md`; `app/index.html`; pergunta 22 em `docs/auditoria/perguntas-pendentes.md`.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-031 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="180" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-032 — Conferir idioma, nomes acessíveis e rótulos</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Inspecionar o idioma declarado no HTML.
+2. Conferir rótulos associados aos campos de endereço.
+3. Conferir nome acessível das ações principais.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENOR</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NÃO FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O documento declara `lang="pt-BR"`; campos e controles exercitados possuem nome acessível programático, e os campos do endereço têm rótulos associados.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: expect(received).toBe(expected) // Object.is equality | Error: campos do endereço devem ter rótulos programáticos | Error: ações principais devem ter nome acessível.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura A11Y-02. Origem: `docs/auditoria/riscos-e-lacunas.md`; perguntas 20 e 22 em `docs/auditoria/perguntas-pendentes.md`.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-032 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="180" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-033 — Verificar compatibilidade nos navegadores suportados</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Abrir a aplicação no Chromium configurado.
+2. Conferir título e catálogo inicial.
+3. Abrir o carrinho.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAIXA</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MENOR</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NÃO FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O navegador suportado pela configuração atual desta suíte é Chromium, que deve completar o fluxo essencial de abertura, catálogo e carrinho.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 1165 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura BROWSER-01. A configuração atual executa Chromium. Pergunta 21 em `docs/auditoria/perguntas-pendentes.md`; origem: `playwright.config.js`.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-033 (PASSOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="180" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CT-034 — Verificar exposição de endereço em logs e evidências</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Montar revisão usando endereço e identificadores sintéticos.
+2. Observar mensagens de console geradas pelo fluxo.
+3. Registrar somente presença/ausência dos marcadores, sem copiar o pedido.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÉDIA</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAIOR</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NÃO FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FALHOU</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs de console gerados ao montar a revisão não devem conter endereço, CEP, complemento ou conteúdo completo do pedido. O teste usa exclusivamente marcadores sintéticos e registra no relatório somente se houve vazamento, sem copiar o texto do pedido.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falhou: Error: console não deve registrar endereço, CEP, complemento ou mensagem completa.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobertura SEC-01 de privacidade. Perguntas 25–26 em `docs/auditoria/perguntas-pendentes.md`; risco R-05 em `docs/auditoria/riscos-e-lacunas.md`; origem: `app/js/app.js`.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-034 (FALHOU); HTML fonte e detalhes no report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="180" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">CT-035 — Conferir integridade estrutural do catálogo local</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cópia local da aplicação; dados e arquivos de imagem disponíveis no workspace.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Percorrer os registros de `app/js/dados.js`.
 2. Conferir unicidade de IDs e presença de categoria, nome, preço numérico e caminho de imagem.
@@ -2287,104 +2556,103 @@
 4. Não validar preço ou conteúdo comercial sem catálogo aprovado.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MÉDIA</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MAIOR</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FUNCIONAL</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PASSOU</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ReferÃªncias estruturais sÃ£o consistentes e caminhos de imagens existentes resolvem para arquivos locais. Validade comercial de nomes e preÃ§os nÃ£o faz parte deste critÃ©rio.</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 23 ms, sem retry.</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referências estruturais são consistentes e caminhos de imagens existentes resolvem para arquivos locais. Validade comercial de nomes e preços não faz parte deste critério.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 35 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura DATA-01. O inventário registra 72 produtos e imagens existentes; confirmar como baseline antes de automatizar a contagem. Pergunta 11 em `docs/auditoria/perguntas-pendentes.md`; origem: `app/js/dados.js`.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Card JPEG — CT-035 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="180" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37" ht="180" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CT-036 — Medir carregamento após definição de orçamento</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ambiente controlado; ambiente, cache, dispositivo, métrica e orçamento de desempenho aprovados.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Definir carregamento frio/quente e dispositivo de referência.
-2. Registrar as métricas acordadas em execuções repetíveis.
-3. Comparar com o orçamento aprovado.
-4. Registrar recursos de maior custo observados.</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cópia local da aplicação em loopback; Chromium; valores sintéticos; integrações externas isoladas conforme o cenário.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Navegar três vezes à cópia local com timeout de 10 s por navegação.
+2. Coletar Navigation Timing.
+3. Comparar medianas com o orçamento de QA documentado.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BAIXA</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MENOR</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NÃO FUNCIONAL</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDENTE</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultado depende de mÃ©trica, ambiente e limite aprovados. Sem esses valores, o cenÃ¡rio Ã© apenas um plano de mediÃ§Ã£o e nÃ£o tem critÃ©rio de aprovaÃ§Ã£o.</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NÃ£o executado. Pendente de critÃ©rio aprovado: mÃ©trica, ambiente e orÃ§amento de desempenho ainda nÃ£o foram definidos.</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASSOU</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contra servidor estático local em loopback, medir três navegações novas e registrar Navigation Timing. A mediana de `domContentLoadedEventEnd` deve ser ≤ 2.500 ms e a mediana de `loadEventEnd` ≤ 5.000 ms. Cada navegação tem timeout máximo de 10 s.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Todas as assertions do caso foram satisfeitas. Playwright Test registrou status passed em 2280 ms, sem retry.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cobertura PERF-01. Nenhum limite de desempenho foi encontrado. Origem: `docs/auditoria/matriz-de-cobertura.md`; `playwright.config.js`.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Card JPEG — CT-036 (PENDENTE); HTML fonte e detalhes no report.html</t>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Card JPEG — CT-036 (PASSOU); HTML fonte e detalhes no report.html</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2690,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId33"/>
   </hyperlinks>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
